--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_RECOLETAS SALUD CARBAJOSA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_RECOLETAS SALUD CARBAJOSA.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. DIEYE</t>
+          <t>E. MADINABEITIA GARCIA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>60.2993</v>
+        <v>59.4786</v>
       </c>
       <c r="E2" t="n">
-        <v>36.1691</v>
+        <v>52.4941</v>
       </c>
       <c r="F2" t="n">
-        <v>24.1305</v>
+        <v>6.9844</v>
       </c>
       <c r="G2" t="n">
-        <v>3.404400000000001</v>
+        <v>33.7519</v>
       </c>
       <c r="H2" t="n">
-        <v>6.366900000000001</v>
+        <v>-0.7050999999999998</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.9628</v>
+        <v>34.4571</v>
       </c>
       <c r="J2" t="n">
-        <v>42.2137</v>
+        <v>71.6541</v>
       </c>
       <c r="K2" t="n">
-        <v>38.9482</v>
+        <v>30.2129</v>
       </c>
       <c r="L2" t="n">
-        <v>3.2659</v>
+        <v>41.4412</v>
       </c>
       <c r="M2" t="n">
-        <v>-38.8091</v>
+        <v>-37.9021</v>
       </c>
       <c r="N2" t="n">
-        <v>-32.581</v>
+        <v>-30.918</v>
       </c>
       <c r="O2" t="n">
-        <v>-6.2282</v>
+        <v>-6.9842</v>
       </c>
       <c r="P2" t="n">
-        <v>-32.4255</v>
+        <v>5.597399999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>-89.3629</v>
+        <v>-54.2352</v>
       </c>
       <c r="R2" t="n">
-        <v>56.9373</v>
+        <v>59.8324</v>
       </c>
       <c r="S2" t="n">
-        <v>60.9135</v>
+        <v>-4.284</v>
       </c>
       <c r="T2" t="n">
-        <v>33.9203</v>
+        <v>-0.4837000000000002</v>
       </c>
       <c r="U2" t="n">
-        <v>26.9932</v>
+        <v>-3.8005</v>
       </c>
       <c r="V2" t="n">
-        <v>28.4068</v>
+        <v>24.4139</v>
       </c>
       <c r="W2" t="n">
-        <v>49.3975</v>
+        <v>35.5589</v>
       </c>
       <c r="X2" t="n">
-        <v>-20.9911</v>
+        <v>-11.1455</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. MADINABEITIA GARCIA</t>
+          <t>A. DIEYE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>37.1919</v>
+        <v>22.0411</v>
       </c>
       <c r="E3" t="n">
-        <v>37.2155</v>
+        <v>13.9794</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.02370000000000028</v>
+        <v>8.0616</v>
       </c>
       <c r="G3" t="n">
-        <v>33.7519</v>
+        <v>3.404400000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.7050999999999998</v>
+        <v>6.366900000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>34.4571</v>
+        <v>-2.9628</v>
       </c>
       <c r="J3" t="n">
-        <v>71.6541</v>
+        <v>42.2137</v>
       </c>
       <c r="K3" t="n">
-        <v>30.2129</v>
+        <v>38.9482</v>
       </c>
       <c r="L3" t="n">
-        <v>41.4412</v>
+        <v>3.2659</v>
       </c>
       <c r="M3" t="n">
-        <v>-37.9021</v>
+        <v>-38.8091</v>
       </c>
       <c r="N3" t="n">
-        <v>-30.918</v>
+        <v>-32.581</v>
       </c>
       <c r="O3" t="n">
-        <v>-6.9842</v>
+        <v>-6.2282</v>
       </c>
       <c r="P3" t="n">
-        <v>5.597399999999999</v>
+        <v>-32.4255</v>
       </c>
       <c r="Q3" t="n">
-        <v>-54.2352</v>
+        <v>-89.3629</v>
       </c>
       <c r="R3" t="n">
-        <v>59.8324</v>
+        <v>56.9373</v>
       </c>
       <c r="S3" t="n">
-        <v>-26.5712</v>
+        <v>22.6551</v>
       </c>
       <c r="T3" t="n">
-        <v>-15.7624</v>
+        <v>11.7308</v>
       </c>
       <c r="U3" t="n">
-        <v>-10.8084</v>
+        <v>10.9243</v>
       </c>
       <c r="V3" t="n">
-        <v>24.4139</v>
+        <v>28.4068</v>
       </c>
       <c r="W3" t="n">
-        <v>35.5589</v>
+        <v>49.3975</v>
       </c>
       <c r="X3" t="n">
-        <v>-11.1455</v>
+        <v>-20.9911</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>29.3192</v>
+        <v>15.7454</v>
       </c>
       <c r="E4" t="n">
-        <v>28.2338</v>
+        <v>12.0149</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0854</v>
+        <v>3.7303</v>
       </c>
       <c r="G4" t="n">
         <v>-1.057600000000001</v>
@@ -766,13 +766,13 @@
         <v>44.5848</v>
       </c>
       <c r="S4" t="n">
-        <v>22.4268</v>
+        <v>8.8529</v>
       </c>
       <c r="T4" t="n">
-        <v>25.9725</v>
+        <v>9.7536</v>
       </c>
       <c r="U4" t="n">
-        <v>-3.5455</v>
+        <v>-0.9006999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>4.283</v>
@@ -799,13 +799,13 @@
         <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>6.722399999999999</v>
+        <v>11.0783</v>
       </c>
       <c r="E5" t="n">
-        <v>7.176500000000001</v>
+        <v>10.3563</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4544000000000003</v>
+        <v>0.7221</v>
       </c>
       <c r="G5" t="n">
         <v>14.2333</v>
@@ -844,13 +844,13 @@
         <v>20.073</v>
       </c>
       <c r="S5" t="n">
-        <v>-5.3759</v>
+        <v>-1.0199</v>
       </c>
       <c r="T5" t="n">
-        <v>-3.1143</v>
+        <v>0.0653999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.2617</v>
+        <v>-1.0853</v>
       </c>
       <c r="V5" t="n">
         <v>6.9363</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. NDIR</t>
+          <t>J. MORAN HUETE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.9334</v>
+        <v>3.765899999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3346</v>
+        <v>11.2471</v>
       </c>
       <c r="F6" t="n">
-        <v>-6.2683</v>
+        <v>-7.481199999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0505</v>
+        <v>0.5992999999999988</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3338</v>
+        <v>-14.5673</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.3842</v>
+        <v>15.1667</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668200000000001</v>
+        <v>19.6967</v>
       </c>
       <c r="K6" t="n">
-        <v>4.1391</v>
+        <v>4.842699999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5291</v>
+        <v>14.8542</v>
       </c>
       <c r="M6" t="n">
-        <v>-5.7186</v>
+        <v>-19.0973</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.8052</v>
+        <v>-19.4099</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.9133</v>
+        <v>0.3122999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.9301</v>
+        <v>23.1611</v>
       </c>
       <c r="Q6" t="n">
-        <v>-10.0363</v>
+        <v>-16.0195</v>
       </c>
       <c r="R6" t="n">
-        <v>8.106199999999999</v>
+        <v>39.1806</v>
       </c>
       <c r="S6" t="n">
-        <v>8.3491</v>
+        <v>-5.7408</v>
       </c>
       <c r="T6" t="n">
-        <v>7.9875</v>
+        <v>-0.8567000000000002</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3615</v>
+        <v>-4.8841</v>
       </c>
       <c r="V6" t="n">
-        <v>-7.3021</v>
+        <v>-14.2535</v>
       </c>
       <c r="W6" t="n">
-        <v>1.7153</v>
+        <v>8.427</v>
       </c>
       <c r="X6" t="n">
-        <v>-9.0175</v>
+        <v>-22.6802</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. DARAME PIZARRO</t>
+          <t>J. DOSS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>-6.4303</v>
+        <v>-2.8746</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2205000000000005</v>
+        <v>-8.583</v>
       </c>
       <c r="F7" t="n">
-        <v>-6.2096</v>
+        <v>5.7084</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.422</v>
+        <v>-1.9657</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3821</v>
+        <v>-0.8067999999999997</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.8043</v>
+        <v>-1.1588</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6345</v>
+        <v>8.7765</v>
       </c>
       <c r="K7" t="n">
-        <v>2.5459</v>
+        <v>9.2453</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0886999999999999</v>
+        <v>-0.4689000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-5.0564</v>
+        <v>-10.7419</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1636</v>
+        <v>-10.0521</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.893</v>
+        <v>-0.6898</v>
       </c>
       <c r="P7" t="n">
-        <v>1.158</v>
+        <v>-6.9483</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.246</v>
+        <v>-25.8631</v>
       </c>
       <c r="R7" t="n">
-        <v>5.404</v>
+        <v>18.9149</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8262999999999999</v>
+        <v>-2.58</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1898</v>
+        <v>-0.8229</v>
       </c>
       <c r="U7" t="n">
-        <v>-2.0162</v>
+        <v>-1.757</v>
       </c>
       <c r="V7" t="n">
-        <v>-4.340000000000001</v>
+        <v>8.6191</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2014</v>
+        <v>9.326599999999999</v>
       </c>
       <c r="X7" t="n">
-        <v>-4.5415</v>
+        <v>-0.7076</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. LOPEZ RAMOS</t>
+          <t>G. DARAME PIZARRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>-7.488300000000001</v>
+        <v>-6.0204</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4185</v>
+        <v>-1.3626</v>
       </c>
       <c r="F8" t="n">
-        <v>-5.0699</v>
+        <v>-4.6579</v>
       </c>
       <c r="G8" t="n">
-        <v>-6.5322</v>
+        <v>-2.422</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.6491</v>
+        <v>1.3821</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.8829</v>
+        <v>-3.8043</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.0216</v>
+        <v>2.6345</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2381</v>
+        <v>2.5459</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.7835</v>
+        <v>0.0886999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.5105</v>
+        <v>-5.0564</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.411</v>
+        <v>-1.1636</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.0994</v>
+        <v>-3.893</v>
       </c>
       <c r="P8" t="n">
-        <v>2.123</v>
+        <v>1.158</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.351</v>
+        <v>-4.246</v>
       </c>
       <c r="R8" t="n">
-        <v>3.474</v>
+        <v>5.404</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6657000000000001</v>
+        <v>-0.4164000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2737999999999999</v>
+        <v>0.0475999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.392</v>
+        <v>-0.4641</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.4138</v>
+        <v>-4.340000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>1.228</v>
+        <v>0.2014</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.6417</v>
+        <v>-4.5415</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. DOSS</t>
+          <t>S. LOPEZ RAMOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>-8.4915</v>
+        <v>-6.7338</v>
       </c>
       <c r="E9" t="n">
-        <v>-10.8585</v>
+        <v>-1.9583</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3668</v>
+        <v>-4.7754</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9657</v>
+        <v>-6.5322</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8067999999999997</v>
+        <v>-2.6491</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1588</v>
+        <v>-3.8829</v>
       </c>
       <c r="J9" t="n">
-        <v>8.7765</v>
+        <v>-2.0216</v>
       </c>
       <c r="K9" t="n">
-        <v>9.2453</v>
+        <v>-0.2381</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.4689000000000001</v>
+        <v>-1.7835</v>
       </c>
       <c r="M9" t="n">
-        <v>-10.7419</v>
+        <v>-4.5105</v>
       </c>
       <c r="N9" t="n">
-        <v>-10.0521</v>
+        <v>-2.411</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6898</v>
+        <v>-2.0994</v>
       </c>
       <c r="P9" t="n">
-        <v>-6.9483</v>
+        <v>2.123</v>
       </c>
       <c r="Q9" t="n">
-        <v>-25.8631</v>
+        <v>-1.351</v>
       </c>
       <c r="R9" t="n">
-        <v>18.9149</v>
+        <v>3.474</v>
       </c>
       <c r="S9" t="n">
-        <v>-8.196999999999999</v>
+        <v>0.08879999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-3.0983</v>
+        <v>0.1865000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-5.0984</v>
+        <v>-0.09760000000000005</v>
       </c>
       <c r="V9" t="n">
-        <v>8.6191</v>
+        <v>-2.4138</v>
       </c>
       <c r="W9" t="n">
-        <v>9.326599999999999</v>
+        <v>1.228</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.7076</v>
+        <v>-3.6417</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. DIEYE</t>
+          <t>M. NDIR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>-10.6375</v>
+        <v>-7.356999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5042</v>
+        <v>-0.7943999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-7.1332</v>
+        <v>-6.5626</v>
       </c>
       <c r="G10" t="n">
-        <v>-6.603800000000001</v>
+        <v>-1.0505</v>
       </c>
       <c r="H10" t="n">
-        <v>-8.955</v>
+        <v>1.3338</v>
       </c>
       <c r="I10" t="n">
-        <v>2.3512</v>
+        <v>-2.3842</v>
       </c>
       <c r="J10" t="n">
-        <v>4.3727</v>
+        <v>4.668200000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.07900000000000018</v>
+        <v>4.1391</v>
       </c>
       <c r="L10" t="n">
-        <v>4.4521</v>
+        <v>0.5291</v>
       </c>
       <c r="M10" t="n">
-        <v>-10.9768</v>
+        <v>-5.7186</v>
       </c>
       <c r="N10" t="n">
-        <v>-8.875999999999999</v>
+        <v>-2.8052</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.1008</v>
+        <v>-2.9133</v>
       </c>
       <c r="P10" t="n">
-        <v>4.6321</v>
+        <v>-1.9301</v>
       </c>
       <c r="Q10" t="n">
-        <v>-15.2474</v>
+        <v>-10.0363</v>
       </c>
       <c r="R10" t="n">
-        <v>19.8798</v>
+        <v>8.106199999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>3.2011</v>
+        <v>2.9256</v>
       </c>
       <c r="T10" t="n">
-        <v>4.3853</v>
+        <v>2.8585</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1841</v>
+        <v>0.06709999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>-11.8671</v>
+        <v>-7.3021</v>
       </c>
       <c r="W10" t="n">
-        <v>2.9855</v>
+        <v>1.7153</v>
       </c>
       <c r="X10" t="n">
-        <v>-14.8526</v>
+        <v>-9.0175</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. MORAN HUETE</t>
+          <t>A. RAMIREZ RUIZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>-15.9986</v>
+        <v>-11.1031</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2760999999999997</v>
+        <v>-13.0617</v>
       </c>
       <c r="F11" t="n">
-        <v>-15.7225</v>
+        <v>1.9584</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5992999999999988</v>
+        <v>-20.6984</v>
       </c>
       <c r="H11" t="n">
-        <v>-14.5673</v>
+        <v>-5.9678</v>
       </c>
       <c r="I11" t="n">
-        <v>15.1667</v>
+        <v>-14.7304</v>
       </c>
       <c r="J11" t="n">
-        <v>19.6967</v>
+        <v>5.5121</v>
       </c>
       <c r="K11" t="n">
-        <v>4.842699999999999</v>
+        <v>14.1703</v>
       </c>
       <c r="L11" t="n">
-        <v>14.8542</v>
+        <v>-8.658200000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-19.0973</v>
+        <v>-26.2102</v>
       </c>
       <c r="N11" t="n">
-        <v>-19.4099</v>
+        <v>-20.1381</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3122999999999999</v>
+        <v>-6.0725</v>
       </c>
       <c r="P11" t="n">
-        <v>23.1611</v>
+        <v>-9.264199999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>-16.0195</v>
+        <v>-48.8308</v>
       </c>
       <c r="R11" t="n">
-        <v>39.1806</v>
+        <v>39.5667</v>
       </c>
       <c r="S11" t="n">
-        <v>-25.5055</v>
+        <v>0.02849999999999997</v>
       </c>
       <c r="T11" t="n">
-        <v>-12.3797</v>
+        <v>1.9071</v>
       </c>
       <c r="U11" t="n">
-        <v>-13.1257</v>
+        <v>-1.878</v>
       </c>
       <c r="V11" t="n">
-        <v>-14.2535</v>
+        <v>18.831</v>
       </c>
       <c r="W11" t="n">
-        <v>8.427</v>
+        <v>28.3506</v>
       </c>
       <c r="X11" t="n">
-        <v>-22.6802</v>
+        <v>-9.5197</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C. HERRERO SANDOVAL</t>
+          <t>M. DIEYE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>-16.6388</v>
+        <v>-13.2614</v>
       </c>
       <c r="E12" t="n">
-        <v>-18.2895</v>
+        <v>-6.232600000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6506</v>
+        <v>-7.0285</v>
       </c>
       <c r="G12" t="n">
-        <v>-20.5024</v>
+        <v>-6.603800000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-6.0978</v>
+        <v>-8.955</v>
       </c>
       <c r="I12" t="n">
-        <v>-14.4045</v>
+        <v>2.3512</v>
       </c>
       <c r="J12" t="n">
-        <v>-9.8535</v>
+        <v>4.3727</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2688999999999999</v>
+        <v>-0.07900000000000018</v>
       </c>
       <c r="L12" t="n">
-        <v>-10.1222</v>
+        <v>4.4521</v>
       </c>
       <c r="M12" t="n">
-        <v>-10.6487</v>
+        <v>-10.9768</v>
       </c>
       <c r="N12" t="n">
-        <v>-6.3667</v>
+        <v>-8.875999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.282100000000001</v>
+        <v>-2.1008</v>
       </c>
       <c r="P12" t="n">
-        <v>7.527100000000001</v>
+        <v>4.6321</v>
       </c>
       <c r="Q12" t="n">
-        <v>-11.1942</v>
+        <v>-15.2474</v>
       </c>
       <c r="R12" t="n">
-        <v>18.7214</v>
+        <v>19.8798</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6054000000000004</v>
+        <v>0.5772</v>
       </c>
       <c r="T12" t="n">
-        <v>1.531</v>
+        <v>1.6567</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.1366</v>
+        <v>-1.0793</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.0583</v>
+        <v>-11.8671</v>
       </c>
       <c r="W12" t="n">
-        <v>1.228</v>
+        <v>2.9855</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.2862</v>
+        <v>-14.8526</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K. DOMINGOS</t>
+          <t>C. HERRERO SANDOVAL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D13" t="n">
-        <v>-20.73</v>
+        <v>-16.4834</v>
       </c>
       <c r="E13" t="n">
-        <v>-13.9515</v>
+        <v>-18.4547</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.7784</v>
+        <v>1.9714</v>
       </c>
       <c r="G13" t="n">
-        <v>-11.6811</v>
+        <v>-20.5024</v>
       </c>
       <c r="H13" t="n">
-        <v>-12.4986</v>
+        <v>-6.0978</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8175000000000001</v>
+        <v>-14.4045</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.753</v>
+        <v>-9.8535</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.2589</v>
+        <v>0.2688999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>1.5059</v>
+        <v>-10.1222</v>
       </c>
       <c r="M13" t="n">
-        <v>-7.9281</v>
+        <v>-10.6487</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.2397</v>
+        <v>-6.3667</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6884000000000001</v>
+        <v>-4.282100000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-6.3693</v>
+        <v>7.527100000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-15.0545</v>
+        <v>-11.1942</v>
       </c>
       <c r="R13" t="n">
-        <v>8.6854</v>
+        <v>18.7214</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4358</v>
+        <v>-0.4505000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>3.4267</v>
+        <v>1.3655</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9910000000000001</v>
+        <v>-1.8162</v>
       </c>
       <c r="V13" t="n">
-        <v>-5.1151</v>
+        <v>-3.0583</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4293</v>
+        <v>1.228</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.5445</v>
+        <v>-4.2862</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. RAMIREZ RUIZ</t>
+          <t>K. DOMINGOS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>-30.3356</v>
+        <v>-22.2786</v>
       </c>
       <c r="E14" t="n">
-        <v>-27.4265</v>
+        <v>-15.6598</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.909</v>
+        <v>-6.6187</v>
       </c>
       <c r="G14" t="n">
-        <v>-20.6984</v>
+        <v>-11.6811</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.9678</v>
+        <v>-12.4986</v>
       </c>
       <c r="I14" t="n">
-        <v>-14.7304</v>
+        <v>0.8175000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>5.5121</v>
+        <v>-3.753</v>
       </c>
       <c r="K14" t="n">
-        <v>14.1703</v>
+        <v>-5.2589</v>
       </c>
       <c r="L14" t="n">
-        <v>-8.658200000000001</v>
+        <v>1.5059</v>
       </c>
       <c r="M14" t="n">
-        <v>-26.2102</v>
+        <v>-7.9281</v>
       </c>
       <c r="N14" t="n">
-        <v>-20.1381</v>
+        <v>-7.2397</v>
       </c>
       <c r="O14" t="n">
-        <v>-6.0725</v>
+        <v>-0.6884000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>-9.264199999999999</v>
+        <v>-6.3693</v>
       </c>
       <c r="Q14" t="n">
-        <v>-48.8308</v>
+        <v>-15.0545</v>
       </c>
       <c r="R14" t="n">
-        <v>39.5667</v>
+        <v>8.6854</v>
       </c>
       <c r="S14" t="n">
-        <v>-19.2036</v>
+        <v>0.8871</v>
       </c>
       <c r="T14" t="n">
-        <v>-12.4578</v>
+        <v>1.7183</v>
       </c>
       <c r="U14" t="n">
-        <v>-6.746</v>
+        <v>-0.8313999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>18.831</v>
+        <v>-5.1151</v>
       </c>
       <c r="W14" t="n">
-        <v>28.3506</v>
+        <v>1.4293</v>
       </c>
       <c r="X14" t="n">
-        <v>-9.5197</v>
+        <v>-6.5445</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>-33.3216</v>
+        <v>-29.7175</v>
       </c>
       <c r="E15" t="n">
-        <v>-29.1432</v>
+        <v>-25.0024</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.178599999999999</v>
+        <v>-4.715299999999999</v>
       </c>
       <c r="G15" t="n">
         <v>-23.9264</v>
@@ -1624,13 +1624,13 @@
         <v>23.3536</v>
       </c>
       <c r="S15" t="n">
-        <v>-4.9681</v>
+        <v>-1.3642</v>
       </c>
       <c r="T15" t="n">
-        <v>-4.7959</v>
+        <v>-0.6554</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1719999999999999</v>
+        <v>-0.7091000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>-4.4272</v>
@@ -1657,13 +1657,13 @@
         <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-64.13380000000001</v>
+        <v>-48.8102</v>
       </c>
       <c r="E16" t="n">
-        <v>-43.0134</v>
+        <v>-31.5684</v>
       </c>
       <c r="F16" t="n">
-        <v>-21.1202</v>
+        <v>-17.2416</v>
       </c>
       <c r="G16" t="n">
         <v>-26.3692</v>
@@ -1702,13 +1702,13 @@
         <v>29.9161</v>
       </c>
       <c r="S16" t="n">
-        <v>-16.1823</v>
+        <v>-0.8587</v>
       </c>
       <c r="T16" t="n">
-        <v>-10.84</v>
+        <v>0.6049000000000002</v>
       </c>
       <c r="U16" t="n">
-        <v>-5.3427</v>
+        <v>-1.464</v>
       </c>
       <c r="V16" t="n">
         <v>-17.5286</v>
@@ -1735,13 +1735,13 @@
         <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>-82.60660000000004</v>
+        <v>-52.5307</v>
       </c>
       <c r="E17" t="n">
-        <v>-35.9724</v>
+        <v>-22.58610000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-46.6345</v>
+        <v>-29.9446</v>
       </c>
       <c r="G17" t="n">
         <v>-70.82040000000001</v>
@@ -1762,7 +1762,7 @@
         <v>42.76409999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-258.8389999999999</v>
+        <v>-258.839</v>
       </c>
       <c r="N17" t="n">
         <v>-210.9289</v>
@@ -1780,16 +1780,16 @@
         <v>396.6302000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>-10.77470000000001</v>
+        <v>19.3007</v>
       </c>
       <c r="T17" t="n">
-        <v>15.69089999999999</v>
+        <v>29.0762</v>
       </c>
       <c r="U17" t="n">
-        <v>-26.4656</v>
+        <v>-9.775899999999998</v>
       </c>
       <c r="V17" t="n">
-        <v>21.18439999999999</v>
+        <v>21.1844</v>
       </c>
       <c r="W17" t="n">
         <v>179.1465</v>
